--- a/Mau_Nhat_ky_mat_dien.xlsx
+++ b/Mau_Nhat_ky_mat_dien.xlsx
@@ -11,20 +11,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KH_mat_dien" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Huong_dan" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Su_co'!$A$1:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'KH_mat_dien'!$A$1:$F$4</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="5">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,17 +31,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <color rgb="000000FF"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0017365D"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <color rgb="00666666"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -57,11 +41,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0017365D"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -69,26 +53,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00D9E2F3"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -463,10 +435,11 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,107 +480,67 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>NGUYEN_NHAN_SAI_SO</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>TY_LE_PHU_TAI_ANH_HUONG</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>GHI_CHU</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SC001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>08/08/2026</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>25/08/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>TBA Mau 1</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Nhanh 1</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Su co luoi dien</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Ví dụ - xóa trước khi dùng</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SC002</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>18/08/2026</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>TBA Mau 2</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Khu vực 2</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cat dien cong tac</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Ví dụ - xóa trước khi dùng</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TBA ...</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Khu vực ...</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Sự cố/CM sửa chữa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Mất điện làm giảm điện thương phẩm</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -618,15 +551,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -647,88 +581,53 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>NGUYEN_NHAN_SAI_SO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>KWH_GIO_UOC_TINH</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CONG_SUAT_KW</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>HE_SO_KHUNG_GIO</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>SC001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>PA07XT0000001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Khách hàng mẫu A</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PA07XT...</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tên khách hàng</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mất điện 3,5 giờ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SC001</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>PA07XT0000002</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Khách hàng mẫu B</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SC002</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>PA07XT0000003</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Khách hàng mẫu C</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="n">
-        <v>1.2</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -739,65 +638,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>EVN Forecast 1.2 - Mẫu nhật ký mất điện</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>EVN Forecast 1.4 - Mẫu nhật ký mất điện / nguyên nhân sai số</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>1. Sheet Su_co: mỗi dòng là một sự kiện mất điện.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sheet Su_co: mỗi dòng là một sự cố. Sheet KH_mat_dien: liệt kê khách hàng bị ảnh hưởng theo SU_CO_ID.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>2. Sheet KH_mat_dien: mỗi dòng là một khách hàng bị ảnh hưởng bởi SU_CO_ID tương ứng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>3. GIO_BAT_DAU/GIO_KET_THUC dùng HH:MM. Nếu giờ kết thúc nhỏ hơn giờ bắt đầu, hệ thống hiểu là qua ngày hôm sau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>4. TY_LE_PHU_TAI_ANH_HUONG nhập 1.0 = 100%, 0.5 = 50%. Chỉ dùng khi sự cố không ảnh hưởng toàn bộ phụ tải trong phạm vi ghi nhận.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>5. KWH_GIO_UOC_TINH và CONG_SUAT_KW là tùy chọn. Nếu bỏ trống, hệ thống ước tính từ lịch sử điện năng khách hàng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>6. HE_SO_KHUNG_GIO là tùy chọn. Ví dụ 1.2 nếu thời gian mất điện đúng giờ cao tải; mặc định 1.0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>7. Xóa các dòng ví dụ trước khi nhập dữ liệu thật.</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nếu không nhập KWH_GIO_UOC_TINH hoặc CONG_SUAT_KW, hệ thống ước tính theo lịch sử tiêu thụ của khách hàng.</t>
         </is>
       </c>
     </row>

--- a/Mau_Nhat_ky_mat_dien.xlsx
+++ b/Mau_Nhat_ky_mat_dien.xlsx
@@ -29,7 +29,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,7 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,7 +59,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -430,16 +429,16 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,7 +511,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -527,18 +526,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sự cố/CM sửa chữa</t>
+          <t>Sự cố/CT sửa chữa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mất điện làm giảm điện thương phẩm</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>100</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>Mất điện làm giảm ĐTP</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TỰ TÍNH TRONG APP</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Không nhập tỷ lệ</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -554,8 +559,8 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -616,15 +621,13 @@
           <t>Tên khách hàng</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mất điện 3,5 giờ</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>1</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -638,30 +641,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EVN Forecast 1.4 - Mẫu nhật ký mất điện / nguyên nhân sai số</t>
+          <t>EVN Forecast 1.5.3 - Mẫu nhật ký mất điện</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sheet Su_co: mỗi dòng là một sự cố. Sheet KH_mat_dien: liệt kê khách hàng bị ảnh hưởng theo SU_CO_ID.</t>
+          <t>Sheet Su_co: mỗi dòng là một sự cố. Sheet KH_mat_dien: danh sách khách hàng bị ảnh hưởng theo SU_CO_ID.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nếu không nhập KWH_GIO_UOC_TINH hoặc CONG_SUAT_KW, hệ thống ước tính theo lịch sử tiêu thụ của khách hàng.</t>
+          <t>Cột TY_LE_PHU_TAI_ANH_HUONG KHÔNG cần nhập. App tự tính = tổng sản lượng tháng của các KH bị ảnh hưởng / tổng sản lượng toàn đơn vị cùng tháng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nếu tháng sự cố chưa có thực tế, app dùng sản lượng tháng gần nhất trước đó để ước tính tỷ lệ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KWH_GIO_UOC_TINH hoặc CONG_SUAT_KW là tùy chọn. Nếu bỏ trống, app ước từ lịch sử tiêu thụ của KH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mỗi lần lưu nhật ký đều được lưu vết; có thể chọn Xóa trong tab Mất điện khi nhập sai.</t>
         </is>
       </c>
     </row>
